--- a/examples/sample_multi_sheet.xlsx
+++ b/examples/sample_multi_sheet.xlsx
@@ -414,21 +414,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gold_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>model_output</t>
         </is>
@@ -437,15 +442,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>7651543994911984990</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>X001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>{"prob_1": 0.12, "reason": "非目标工作表"}</t>
         </is>
@@ -462,21 +472,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gold_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>model_output</t>
         </is>
@@ -485,66 +500,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>7651543994911984911</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>S101</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>target_a</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{"prob_1": 0.96, "prob_2": 0.04, "reason": "示例说明A"}</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{"prob_1": 0.96, "prob_2": 0.04, "reason": "示例说明A", "items": ["item_a", "item_b", "item_c"]}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>7651543994911984912</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>S102</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>target_a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{"prob_1": 0.84, "prob_2": 0.16, "reason": "示例说明B"}</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{"prob_1": 0.84, "prob_2": 0.16, "reason": "示例说明B", "items": ["item_a"]}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>7651543994911984913</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>S103</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>target_b</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{"prob_1": 0.28, "prob_2": 0.72, "reason": "示例说明C"}</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"prob_1": 0.28, "prob_2": 0.72, "reason": "示例说明C", "items": []}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>7651543994911984914</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>S104</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>target_c</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>{"prob_1": 0.11, "prob_2": 0.89, "reason": "示例说明D"}</t>
         </is>
@@ -553,15 +588,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>7651543994911984915</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>S105</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>target_a</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
